--- a/timetable_generator/timetable_outputs/ECE_Sem1_SectionA_Timetable.xlsx
+++ b/timetable_generator/timetable_outputs/ECE_Sem1_SectionA_Timetable.xlsx
@@ -466,21 +466,23 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>HS152
-Economics/IET
-C101
-Dr. Anushree Kini</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EC161
+DigitaL Design
+C101
+Dr. Prakash Pawar
+[COMMON]</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CS161
-Problem solving through programming
-C101
-Dr. Animesh Roy</t>
+          <t>EC161
+DigitaL Design
+C101
+Dr. Prakash Pawar
+[COMMON]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -492,32 +494,19 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>EC161
-DigitaL Design
-C101
-Dr. Prakash Pawar</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>HS152
-Economics/IET
-C101
-Dr. Anushree Kini</t>
-        </is>
-      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CS161
+Problem solving through programming
+C101
+Dr. Animesh Roy
+[COMMON]</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>EC161
-DigitaL Design
-C101
-Dr. Prakash Pawar</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -525,25 +514,35 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CS161
+Problem solving through programming
+C101
+Dr. Animesh Roy
+[COMMON]</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>HS152
+Economics/IET
+C101
+Dr. Anushree Kini
+[COMMON]</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CS161
-Problem solving through programming
-C101
-Dr. Animesh Roy</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
           <t>EC161
 DigitaL Design
 C101
-Dr. Prakash Pawar</t>
-        </is>
-      </c>
+Dr. Prakash Pawar
+[COMMON]</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -552,15 +551,16 @@
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>CS161
-Problem solving through programming
-C101
-Dr. Animesh Roy</t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>HS152
+Economics/IET
+C101
+Dr. Anushree Kini
+[COMMON]</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
     </row>
@@ -572,7 +572,15 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CS161
+Problem solving through programming
+C101
+Dr. Animesh Roy
+[COMMON]</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
     </row>
